--- a/data.xlsx
+++ b/data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Enroll</t>
   </si>
@@ -30,16 +30,49 @@
     <t>Marks</t>
   </si>
   <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Jane</t>
-  </si>
-  <si>
-    <t>Alice</t>
-  </si>
-  <si>
-    <t>Anne</t>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>Linux</t>
+  </si>
+  <si>
+    <t>Sem</t>
+  </si>
+  <si>
+    <t>TD1</t>
+  </si>
+  <si>
+    <t>Jack Linc</t>
+  </si>
+  <si>
+    <t>Jane Hopper</t>
+  </si>
+  <si>
+    <t>Anne Bell</t>
+  </si>
+  <si>
+    <t>Kristine Kaley</t>
+  </si>
+  <si>
+    <t>Erik Bodland</t>
+  </si>
+  <si>
+    <t>Alice Thump</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>Yash Jyoti</t>
+  </si>
+  <si>
+    <t>Hari Prakash</t>
+  </si>
+  <si>
+    <t>Niharika Teling</t>
+  </si>
+  <si>
+    <t>Bob Hupe</t>
   </si>
 </sst>
 </file>
@@ -75,8 +108,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -371,77 +407,190 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="2" width="8.7265625" style="1"/>
+    <col min="3" max="3" width="12.54296875" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.7265625" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
+    <row r="5" spans="1:4">
+      <c r="A5" s="1">
         <v>1001</v>
       </c>
-      <c r="B2">
+      <c r="B5" s="1">
         <v>5001</v>
       </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2">
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1">
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
+    <row r="6" spans="1:4">
+      <c r="A6" s="1">
         <v>1002</v>
       </c>
-      <c r="B3">
+      <c r="B6" s="1">
         <v>5002</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3">
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="1">
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
+    <row r="7" spans="1:4">
+      <c r="A7" s="1">
         <v>1003</v>
       </c>
-      <c r="B4">
+      <c r="B7" s="1">
         <v>5003</v>
       </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4">
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
+    <row r="8" spans="1:4">
+      <c r="A8" s="1">
         <v>1004</v>
       </c>
-      <c r="B5">
+      <c r="B8" s="1">
         <v>5004</v>
       </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5">
+      <c r="C8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="1">
         <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1">
+        <v>1005</v>
+      </c>
+      <c r="B9" s="1">
+        <v>5005</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1">
+        <v>1006</v>
+      </c>
+      <c r="B10" s="1">
+        <v>5006</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1">
+        <v>1007</v>
+      </c>
+      <c r="B11" s="1">
+        <v>5007</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1">
+        <v>1008</v>
+      </c>
+      <c r="B12" s="1">
+        <v>5008</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1">
+        <v>1009</v>
+      </c>
+      <c r="B13" s="1">
+        <v>5009</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1">
+        <v>1010</v>
+      </c>
+      <c r="B14" s="1">
+        <v>5010</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="1">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
